--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486720_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486720_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.647600000000001</v>
+        <v>9.497400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1127</v>
+        <v>5.9128</v>
       </c>
       <c r="F2" t="n">
-        <v>3.535</v>
+        <v>3.5846</v>
       </c>
       <c r="G2" t="n">
         <v>7.9622</v>
@@ -610,13 +610,13 @@
         <v>3.4754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4191</v>
+        <v>0.2689</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3856</v>
+        <v>0.1857</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0336</v>
+        <v>0.0832</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0852</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8946</v>
+        <v>4.8063</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0727</v>
+        <v>2.183</v>
       </c>
       <c r="F3" t="n">
-        <v>2.822</v>
+        <v>2.6233</v>
       </c>
       <c r="G3" t="n">
         <v>1.7171</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8606</v>
+        <v>0.7723</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4959</v>
+        <v>0.6063</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3647</v>
+        <v>0.166</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ BRUNO</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1449</v>
+        <v>3.1172</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9722</v>
+        <v>1.9668</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1728</v>
+        <v>1.1503</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3731</v>
+        <v>0.4799</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7724</v>
+        <v>1.8204</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3994</v>
+        <v>-1.3406</v>
       </c>
       <c r="J4" t="n">
-        <v>1.374</v>
+        <v>0.7917</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2903</v>
+        <v>1.4766</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0837</v>
+        <v>-0.6849</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0009</v>
+        <v>-0.3118</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4821</v>
+        <v>0.3439</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.483</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2352</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1854</v>
+        <v>0.5581</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0498</v>
+        <v>0.3728</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5712</v>
+        <v>1.5133</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5712</v>
+        <v>2.741</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>J. MARTÍNEZ BRUNO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1295</v>
+        <v>2.7921</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9047</v>
+        <v>1.4207</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2248</v>
+        <v>1.3714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4799</v>
+        <v>0.3731</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8204</v>
+        <v>1.7724</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3406</v>
+        <v>-1.3994</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7917</v>
+        <v>1.374</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4766</v>
+        <v>1.2903</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6849</v>
+        <v>0.0837</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3118</v>
+        <v>-1.0009</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3439</v>
+        <v>0.4821</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.483</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9433</v>
+        <v>0.8824</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4959</v>
+        <v>0.6339</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4473</v>
+        <v>0.2485</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5133</v>
+        <v>0.5712</v>
       </c>
       <c r="W5" t="n">
-        <v>2.741</v>
+        <v>0.5712</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3886</v>
+        <v>0.4838</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0849</v>
+        <v>-0.1883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4735</v>
+        <v>0.6722</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4787</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1987</v>
+        <v>-0.1034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2756</v>
+        <v>0.1721</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4742</v>
+        <v>-0.2756</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5443</v>
+        <v>-0.2808</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4116</v>
+        <v>-0.1979</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1326</v>
+        <v>-0.083</v>
       </c>
       <c r="G7" t="n">
         <v>0.0847</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0497</v>
+        <v>0.2137</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.138</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0883</v>
+        <v>0.138</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1631</v>
+        <v>-0.8707</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8219</v>
+        <v>-1.5047</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1054</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5131</v>
+        <v>-0.2207</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4139</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.124</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1591</v>
+        <v>-2.9619</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7103</v>
+        <v>-2.2897</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4487</v>
+        <v>-0.6722</v>
       </c>
       <c r="G9" t="n">
         <v>-3.1936</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.066</v>
+        <v>0.1311</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3863</v>
+        <v>0.0344</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3202</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3177</v>
+        <v>-3.2004</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0139</v>
+        <v>-2.8966</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3038</v>
@@ -1234,10 +1234,10 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4136</v>
+        <v>0.5309</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2756</v>
+        <v>0.3929</v>
       </c>
       <c r="U10" t="n">
         <v>0.138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1884</v>
+        <v>-3.2907</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7926</v>
+        <v>-2.0686</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3959</v>
+        <v>-1.2221</v>
       </c>
       <c r="G11" t="n">
         <v>0.7978</v>
@@ -1312,13 +1312,13 @@
         <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9323</v>
+        <v>-0.0346</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6623</v>
+        <v>0.0616</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.27</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-4.0539</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1768</v>
+        <v>-6.0569</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3334</v>
+        <v>-3.0644</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8435</v>
+        <v>-2.9925</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8358</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0441</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4139</v>
+        <v>-0.145</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3698</v>
+        <v>0.2208</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2969</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.655799999999999</v>
+        <v>4.035400000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1063</v>
+        <v>-0.7268999999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7624</v>
+        <v>4.7622</v>
       </c>
       <c r="G13" t="n">
         <v>2.069999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>17.3771</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0679</v>
+        <v>3.4473</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0996</v>
+        <v>2.4791</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9683999999999999</v>
+        <v>0.9682000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-6.3088</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8668</v>
+        <v>5.3755</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6997</v>
+        <v>1.2168</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1672</v>
+        <v>4.1587</v>
       </c>
       <c r="G14" t="n">
         <v>4.0677</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9153</v>
+        <v>-0.4066</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9106</v>
+        <v>-0.3935</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0047</v>
+        <v>-0.0131</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6828</v>
+        <v>4.0028</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1566</v>
+        <v>1.3635</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5262</v>
+        <v>2.6393</v>
       </c>
       <c r="G15" t="n">
         <v>1.6593</v>
@@ -1624,13 +1624,13 @@
         <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1542</v>
+        <v>0.1657</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1217</v>
+        <v>0.2348</v>
       </c>
       <c r="V15" t="n">
         <v>1.5985</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9553</v>
+        <v>2.9868</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4432</v>
+        <v>4.0637</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4879</v>
+        <v>-1.0769</v>
       </c>
       <c r="G16" t="n">
         <v>0.8966</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5005</v>
+        <v>-0.469</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6898</v>
+        <v>-0.0693</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8107</v>
+        <v>-0.3997</v>
       </c>
       <c r="V16" t="n">
         <v>4.2969</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6503</v>
+        <v>2.1207</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8073</v>
+        <v>2.7039</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.157</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>2.7346</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.822</v>
+        <v>-0.3517</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1934</v>
+        <v>-0.2969</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6286</v>
+        <v>-0.0548</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0.1252</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0483</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0493</v>
+        <v>0.1734</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8209</v>
@@ -1858,13 +1858,13 @@
         <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0276</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0828</v>
+        <v>0.2069</v>
       </c>
       <c r="V18" t="n">
         <v>0.6565</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. ABITBOL VIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7972</v>
+        <v>-2.8819</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7618</v>
+        <v>-0.4016</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9646</v>
+        <v>-2.4803</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.701</v>
+        <v>-3.2441</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2413</v>
+        <v>-0.945</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5402</v>
+        <v>-2.2991</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8999</v>
+        <v>-1.3529</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.551</v>
+        <v>0.0215</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6511</v>
+        <v>-1.3744</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8011</v>
+        <v>-1.8912</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6903</v>
+        <v>-0.9665</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1108</v>
+        <v>-0.9247</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7031</v>
+        <v>1.9308</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.0546</v>
+        <v>-0.3862</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3792</v>
+        <v>-0.0553</v>
       </c>
       <c r="T19" t="n">
-        <v>0.965</v>
+        <v>0.1098</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4142</v>
+        <v>-0.1651</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W19" t="n">
         <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ABITBOL VIERA</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9649</v>
+        <v>-3.1764</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4258</v>
+        <v>-4.2789</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3906</v>
+        <v>1.1025</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2441</v>
+        <v>-2.701</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.945</v>
+        <v>-3.2413</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2991</v>
+        <v>0.5402</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3529</v>
+        <v>-1.8999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0215</v>
+        <v>-2.551</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3744</v>
+        <v>0.6511</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8912</v>
+        <v>-0.8011</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9665</v>
+        <v>-0.6903</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9247</v>
+        <v>-0.1108</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9308</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3862</v>
+        <v>-4.0546</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1383</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9371</v>
+        <v>0.4479</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0754</v>
+        <v>0.5521</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="W20" t="n">
         <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0806</v>
+        <v>-4.4505</v>
       </c>
       <c r="E21" t="n">
         <v>-4.0876</v>
       </c>
       <c r="F21" t="n">
-        <v>0.007</v>
+        <v>-0.3628</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0056</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3425</v>
+        <v>-0.0274</v>
       </c>
       <c r="T21" t="n">
         <v>-0.359</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7015</v>
+        <v>0.3316</v>
       </c>
       <c r="V21" t="n">
         <v>0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9694</v>
+        <v>-4.6895</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3971</v>
+        <v>-5.2937</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4277</v>
+        <v>0.6041</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6565</v>
@@ -2170,13 +2170,13 @@
         <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2316</v>
+        <v>0.0482</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3314</v>
+        <v>-0.228</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0998</v>
+        <v>0.2763</v>
       </c>
       <c r="V22" t="n">
         <v>0.0426</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.655899999999999</v>
+        <v>-0.5872999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7622</v>
+        <v>-4.762200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2.106500000000001</v>
+        <v>4.1748</v>
       </c>
       <c r="G23" t="n">
         <v>-2.069899999999999</v>
@@ -2224,7 +2224,7 @@
         <v>3.5612</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.0967</v>
+        <v>-3.096700000000001</v>
       </c>
       <c r="L23" t="n">
         <v>6.657900000000001</v>
@@ -2248,13 +2248,13 @@
         <v>12.55</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0678</v>
+        <v>0.0004999999999999241</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9683999999999999</v>
+        <v>-0.9684999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0994</v>
+        <v>0.969</v>
       </c>
       <c r="V23" t="n">
         <v>6.3089</v>
